--- a/site/exports/nku-philosophy.xlsx
+++ b/site/exports/nku-philosophy.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,13 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="54.59999999999999" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>哲学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>原教授、博士生导师；博士生导师为指导他人资格，不等本人师承。岗位原年写作“202 5至今”，规范起点未知，不自改字形或认证实时现任。；四段本人教育资格原文保留，授位日期未单独核实；两项博士学校不同，不合并事件，不以结束月推授位日。；芝加哥大学两段旁听共十门课程，不是每段十门，不是两学位。主修政治哲学、副修思想文化史保留，未另建副修学位。；张灏分别为香港科大硕士/博士论文来源报告导师，Jimmy Klausen为威斯康星博士论文来源报告导师；没有读取原论文，关系不认证法律或文件真伪。；答辩委员会原列Edward Friedman、John Zumbrunnen、Johann Sommerville、Daniel Kapust、洪长泰、黄敏浩、朱鸿霖；仅委员，不新增导师关系。；两作品原成果列目未列完整作者或著编贡献，不推独著；原2016年10月书籍与2025年8月期刊论文类别分别保留。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -603,7 +657,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="54.59999999999999" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -1067,8 +1121,453 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1998-07</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>原1994年9月至1998年7月，南京大学，学士；授位日期未单列，不把区间末月当授位日。 官网本人具体学位资格列举按来源报告获授；未独立核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>香港科技大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1998-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2000-08</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原1998年9月至2000年8月，香港科技大学，硕士；授位日期未单列，不把区间末月当授位日。 官网本人具体学位资格列举按来源报告获授；未独立核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>香港科技大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2000-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2005-01</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原2000年9月至2005年1月，香港科技大学，博士；授位日期未单列，不把区间末月当授位日。 官网本人具体学位资格列举按来源报告获授；未独立核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>威斯康星大学麦迪逊校区</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2008-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>政治哲学</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>原2008年9月至2014年6月，威斯康星大学麦迪逊校区，博士；授位日期未单列，不把区间末月当授位日。主修政治哲学，副修思想文化史。 官网本人具体学位资格列举按来源报告获授；未独立核验学位证书。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>nondegree_course_auditing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>课程旁听</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>芝加哥大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>芝加哥大学社会思想委员会及政治学系两段旁听：2006年9月至2008年1月、2011年9月至2012年6月，合计十门课程，不是每段十门，不作学位或连续区间。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>教授，博士生导师</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>南开大学哲学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>原任职时段写作“202 5至今”，不擅去空格规范起年；教授为职称，博士生导师为指导他人资格，不新造岗位或本人师承；实时在岗未核。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>北京大学人文社会科学研究院</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>原工作经历栏目2023.9—2023.12北京大学人文社会科学研究院访问学者，不改成求学或学位。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1076,6 +1575,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1087,18 +1593,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18.2" customWidth="1" min="2" max="2"/>
+    <col width="16.8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1166,8 +1672,163 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>张灏</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>硕士论文导师（来源报告）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：诚信与务实 —试论郭嵩焘的外交思想。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>导师当前任职未独立核验。；明确事件绑定；关联经历ID：["nku-fanguangxin-philosophy-education-2"]；关系明确机构：香港科技大学；指导起止：起始时间未披露 至 结束时间未披露；官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：诚信与务实 —试论郭嵩焘的外交思想。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>张灏</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>博士论文导师（来源报告）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：以经术为治术 —晚清湖南理学家“经世”观念研究。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>导师当前任职未独立核验。；明确事件绑定；关联经历ID：["nku-fanguangxin-philosophy-education-3"]；关系明确机构：香港科技大学；指导起止：起始时间未披露 至 结束时间未披露；官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：以经术为治术 —晚清湖南理学家“经世”观念研究。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jimmy Klausen</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>博士论文导师（来源报告）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：Contesting the truth of revolution, democracy and good governance in the land of Confucius: the Chinese reception of Rousseau's The Social Contract, 1898-1906。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>导师当前任职未独立核验。；明确事件绑定；关联经历ID：["nku-fanguangxin-philosophy-education-4"]；关系明确机构：威斯康星大学麦迪逊校区；指导起止：起始时间未披露 至 结束时间未披露；官网本人履历的具名论文指导老师陈述，未读或鉴定原始论文。 论文题名：Contesting the truth of revolution, democracy and good governance in the land of Confucius: the Chinese reception of Rousseau's The Social Contract, 1898-1906。 机构仅为本人该论文阶段所在机构，不独立认证导师单位或现职。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1178,19 +1839,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="54.59999999999999" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="54.59999999999999" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="54.59999999999999" customWidth="1" min="8" max="8"/>
-    <col width="61.59999999999999" customWidth="1" min="9" max="9"/>
-    <col width="54.59999999999999" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1369,8 +2030,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>以经术为治术：晚清湖南理学家的经世思想</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>monograph</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>官网书目，未核出版者元数据或全文；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>个人主要著作或成果列目，完整作者表和具体著编贡献未披露，不推独著；南京大学出版社，2016年10月。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>施特劳斯论民主制与德性—以&lt;城邦与人&gt;为中心</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>官网书目，未核出版者元数据或全文；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>个人主要著作或成果列目，完整作者表和具体著编贡献未披露，不推独著；现代哲学，2025年8月。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1378,6 +2143,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1389,13 +2158,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="39.2" customWidth="1" min="2" max="2"/>
-    <col width="57.4" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="53.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1537,12 +2306,50 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>范广欣</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>nku-2-387</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://rac.nankai.edu.cn/2025/0925/c37504a578478/page.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nku</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
